--- a/Team-Data/2014-15/1-27-2014-15.xlsx
+++ b/Team-Data/2014-15/1-27-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>7.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -769,13 +836,13 @@
         <v>8</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
         <v>13</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -930,7 +997,7 @@
         <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH3" t="n">
         <v>6</v>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
@@ -972,7 +1039,7 @@
         <v>14</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
         <v>16</v>
@@ -981,19 +1048,19 @@
         <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY3" t="n">
         <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
@@ -1118,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
         <v>25</v>
@@ -1154,13 +1221,13 @@
         <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="n">
         <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
         <v>23</v>
@@ -1172,10 +1239,10 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC4" t="n">
         <v>25</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1324,13 +1391,13 @@
         <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1348,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.638</v>
+        <v>0.63</v>
       </c>
       <c r="H6" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J6" t="n">
-        <v>82.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.444</v>
@@ -1416,40 +1483,40 @@
         <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="O6" t="n">
         <v>20.8</v>
       </c>
       <c r="P6" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.784</v>
+        <v>0.782</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="S6" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="T6" t="n">
-        <v>45.6</v>
+        <v>45.3</v>
       </c>
       <c r="U6" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V6" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W6" t="n">
         <v>6.3</v>
       </c>
       <c r="X6" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Y6" t="n">
         <v>5.5</v>
@@ -1458,19 +1525,19 @@
         <v>18.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>101.8</v>
       </c>
       <c r="AC6" t="n">
         <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
@@ -1479,13 +1546,13 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AI6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK6" t="n">
         <v>19</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1509,19 +1576,19 @@
         <v>3</v>
       </c>
       <c r="AR6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="n">
         <v>5</v>
       </c>
-      <c r="AS6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4</v>
-      </c>
       <c r="AU6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1539,7 +1606,7 @@
         <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1589,43 +1656,43 @@
         <v>37.2</v>
       </c>
       <c r="J7" t="n">
-        <v>82.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L7" t="n">
         <v>8.6</v>
       </c>
       <c r="M7" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O7" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P7" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.758</v>
+        <v>0.755</v>
       </c>
       <c r="R7" t="n">
         <v>11.3</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T7" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V7" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W7" t="n">
         <v>7.2</v>
@@ -1634,34 +1701,34 @@
         <v>4.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.8</v>
+        <v>101.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>17</v>
@@ -1679,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP7" t="n">
         <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU7" t="n">
         <v>12</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
         <v>27</v>
@@ -1718,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -1780,19 +1847,19 @@
         <v>9.4</v>
       </c>
       <c r="M8" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O8" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P8" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="R8" t="n">
         <v>10.7</v>
@@ -1807,7 +1874,7 @@
         <v>23.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
@@ -1816,22 +1883,22 @@
         <v>4.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Z8" t="n">
         <v>20.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.6</v>
+        <v>107.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1840,16 +1907,16 @@
         <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1858,19 +1925,19 @@
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN8" t="n">
         <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
@@ -1879,7 +1946,7 @@
         <v>22</v>
       </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1906,7 +1973,7 @@
         <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2025,16 +2092,16 @@
         <v>20</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL9" t="n">
         <v>14</v>
@@ -2046,7 +2113,7 @@
         <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP9" t="n">
         <v>3</v>
@@ -2061,19 +2128,19 @@
         <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV9" t="n">
         <v>13</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>14</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
         <v>27</v>
@@ -2082,10 +2149,10 @@
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
         <v>22</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="n">
         <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>0.37</v>
+        <v>0.378</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,7 +2202,7 @@
         <v>36.6</v>
       </c>
       <c r="J10" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0.426</v>
@@ -2156,31 +2223,31 @@
         <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7</v>
+        <v>0.699</v>
       </c>
       <c r="R10" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S10" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T10" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="U10" t="n">
         <v>21.2</v>
       </c>
       <c r="V10" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
         <v>7.8</v>
       </c>
       <c r="X10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z10" t="n">
         <v>19.2</v>
@@ -2189,13 +2256,13 @@
         <v>19.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2204,16 +2271,16 @@
         <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
@@ -2225,7 +2292,7 @@
         <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
         <v>24</v>
@@ -2249,19 +2316,19 @@
         <v>16</v>
       </c>
       <c r="AV10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -2299,58 +2366,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
         <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0.837</v>
+        <v>0.857</v>
       </c>
       <c r="H11" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="J11" t="n">
-        <v>86.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.484</v>
+        <v>0.486</v>
       </c>
       <c r="L11" t="n">
         <v>10.3</v>
       </c>
       <c r="M11" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.387</v>
+        <v>0.39</v>
       </c>
       <c r="O11" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.778</v>
+        <v>0.781</v>
       </c>
       <c r="R11" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S11" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="T11" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="U11" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="V11" t="n">
         <v>15.1</v>
@@ -2359,13 +2426,13 @@
         <v>9.4</v>
       </c>
       <c r="X11" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA11" t="n">
         <v>19</v>
@@ -2374,10 +2441,10 @@
         <v>111.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2389,13 +2456,13 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2404,19 +2471,19 @@
         <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR11" t="n">
         <v>24</v>
@@ -2434,7 +2501,7 @@
         <v>25</v>
       </c>
       <c r="AW11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -2481,52 +2548,52 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J12" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L12" t="n">
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O12" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.717</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T12" t="n">
         <v>43.4</v>
@@ -2538,7 +2605,7 @@
         <v>17.4</v>
       </c>
       <c r="W12" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X12" t="n">
         <v>4.5</v>
@@ -2547,37 +2614,37 @@
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.9</v>
+        <v>103</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
         <v>13</v>
       </c>
       <c r="AI12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
         <v>21</v>
@@ -2589,19 +2656,19 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
         <v>21</v>
@@ -2610,7 +2677,7 @@
         <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2622,16 +2689,16 @@
         <v>20</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -2663,25 +2730,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" t="n">
         <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>0.34</v>
+        <v>0.348</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J13" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0.429</v>
@@ -2693,7 +2760,7 @@
         <v>20.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.326</v>
+        <v>0.325</v>
       </c>
       <c r="O13" t="n">
         <v>16.2</v>
@@ -2702,19 +2769,19 @@
         <v>21.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R13" t="n">
         <v>10.9</v>
       </c>
       <c r="S13" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T13" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V13" t="n">
         <v>14.7</v>
@@ -2732,16 +2799,16 @@
         <v>21.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="AC13" t="n">
-        <v>-2.4</v>
+        <v>-2.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2753,19 +2820,19 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2780,7 +2847,7 @@
         <v>24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
         <v>14</v>
@@ -2801,19 +2868,19 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2941,10 +3008,10 @@
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -3042,28 +3109,28 @@
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J15" t="n">
-        <v>85.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M15" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O15" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
       </c>
       <c r="Q15" t="n">
         <v>0.744</v>
@@ -3072,10 +3139,10 @@
         <v>11.4</v>
       </c>
       <c r="S15" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T15" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U15" t="n">
         <v>20.5</v>
@@ -3093,25 +3160,25 @@
         <v>4.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB15" t="n">
         <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.6</v>
+        <v>-6.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
@@ -3123,28 +3190,28 @@
         <v>18</v>
       </c>
       <c r="AJ15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
         <v>11</v>
@@ -3159,22 +3226,22 @@
         <v>22</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA15" t="n">
         <v>17</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>21</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -3209,52 +3276,52 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
         <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0.733</v>
+        <v>0.727</v>
       </c>
       <c r="H16" t="n">
         <v>49</v>
       </c>
       <c r="I16" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J16" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.348</v>
       </c>
       <c r="O16" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P16" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q16" t="n">
         <v>0.78</v>
       </c>
       <c r="R16" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S16" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T16" t="n">
         <v>42.7</v>
@@ -3266,28 +3333,28 @@
         <v>13.1</v>
       </c>
       <c r="W16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB16" t="n">
-        <v>101.7</v>
+        <v>101.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3317,7 +3384,7 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
@@ -3326,7 +3393,7 @@
         <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
         <v>23</v>
@@ -3347,19 +3414,19 @@
         <v>8</v>
       </c>
       <c r="AX16" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AY16" t="n">
         <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
         <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>0.444</v>
+        <v>0.455</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="J17" t="n">
         <v>74.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L17" t="n">
         <v>6.9</v>
@@ -3427,49 +3494,49 @@
         <v>17.7</v>
       </c>
       <c r="P17" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T17" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="U17" t="n">
         <v>19.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
         <v>8.1</v>
       </c>
       <c r="X17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y17" t="n">
         <v>4.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>93.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>-3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3502,7 +3569,7 @@
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3520,16 +3587,16 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>9</v>
       </c>
       <c r="AX17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -3538,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18" t="n">
         <v>22</v>
       </c>
       <c r="G18" t="n">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
@@ -3591,43 +3658,43 @@
         <v>37.7</v>
       </c>
       <c r="J18" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.374</v>
+        <v>0.37</v>
       </c>
       <c r="O18" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R18" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S18" t="n">
         <v>30.8</v>
       </c>
       <c r="T18" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U18" t="n">
         <v>23.5</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="W18" t="n">
         <v>9.4</v>
@@ -3636,34 +3703,34 @@
         <v>4.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z18" t="n">
         <v>22.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
         <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI18" t="n">
         <v>14</v>
@@ -3675,13 +3742,13 @@
         <v>8</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO18" t="n">
         <v>25</v>
@@ -3690,13 +3757,13 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3708,13 +3775,13 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX18" t="n">
         <v>15</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ18" t="n">
         <v>29</v>
@@ -3726,7 +3793,7 @@
         <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-9.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3845,13 +3912,13 @@
         <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>19</v>
       </c>
       <c r="AJ19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3866,13 +3933,13 @@
         <v>22</v>
       </c>
       <c r="AO19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -3937,85 +4004,85 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
         <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.523</v>
+        <v>0.533</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>83.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>6.5</v>
       </c>
       <c r="M20" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O20" t="n">
         <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.763</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="S20" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="U20" t="n">
         <v>21.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W20" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.3</v>
+        <v>100.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4033,55 +4100,55 @@
         <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP20" t="n">
         <v>18</v>
       </c>
-      <c r="AP20" t="n">
-        <v>20</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
         <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
         <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>17</v>
@@ -4254,7 +4321,7 @@
         <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>1.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF22" t="n">
         <v>15</v>
@@ -4391,13 +4458,13 @@
         <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
         <v>15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK22" t="n">
         <v>22</v>
@@ -4418,7 +4485,7 @@
         <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR22" t="n">
         <v>4</v>
@@ -4436,7 +4503,7 @@
         <v>22</v>
       </c>
       <c r="AW22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX22" t="n">
         <v>3</v>
@@ -4445,16 +4512,16 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB22" t="n">
         <v>18</v>
       </c>
       <c r="BC22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -4483,82 +4550,82 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>0.319</v>
+        <v>0.313</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
         <v>0.364</v>
       </c>
       <c r="O23" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="P23" t="n">
         <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>40.1</v>
+        <v>40.4</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.7</v>
+        <v>-6</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4582,16 +4649,16 @@
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM23" t="n">
         <v>23</v>
       </c>
       <c r="AN23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4600,7 +4667,7 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
@@ -4612,10 +4679,10 @@
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
@@ -4624,7 +4691,7 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-12.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4779,13 +4846,13 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>27</v>
@@ -4812,7 +4879,7 @@
         <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4943,7 +5010,7 @@
         <v>3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK25" t="n">
         <v>6</v>
@@ -4958,7 +5025,7 @@
         <v>10</v>
       </c>
       <c r="AO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
@@ -4991,7 +5058,7 @@
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -5107,10 +5174,10 @@
         <v>5.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF26" t="n">
         <v>4</v>
@@ -5119,13 +5186,13 @@
         <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK26" t="n">
         <v>18</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5170,7 +5237,7 @@
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
@@ -5182,7 +5249,7 @@
         <v>7</v>
       </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -5298,13 +5365,13 @@
         <v>20</v>
       </c>
       <c r="AG27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH27" t="n">
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5334,7 +5401,7 @@
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5361,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>20</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -5393,43 +5460,43 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.622</v>
+        <v>0.63</v>
       </c>
       <c r="H28" t="n">
         <v>49</v>
       </c>
       <c r="I28" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>83.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.365</v>
+        <v>0.369</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0.767</v>
@@ -5438,22 +5505,22 @@
         <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5468,31 +5535,31 @@
         <v>101.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
         <v>10</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5504,10 +5571,10 @@
         <v>7</v>
       </c>
       <c r="AO28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>11</v>
@@ -5516,16 +5583,16 @@
         <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>16</v>
@@ -5537,10 +5604,10 @@
         <v>15</v>
       </c>
       <c r="AZ28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
         <v>15</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F29" t="n">
         <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>0.667</v>
+        <v>0.659</v>
       </c>
       <c r="H29" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J29" t="n">
-        <v>84.5</v>
+        <v>84.8</v>
       </c>
       <c r="K29" t="n">
         <v>0.456</v>
@@ -5602,25 +5669,25 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="N29" t="n">
         <v>0.346</v>
       </c>
       <c r="O29" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="P29" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="Q29" t="n">
         <v>0.779</v>
       </c>
       <c r="R29" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
         <v>42</v>
@@ -5641,40 +5708,40 @@
         <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA29" t="n">
         <v>21.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>105.7</v>
+        <v>105.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF29" t="n">
         <v>7</v>
       </c>
       <c r="AG29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI29" t="n">
         <v>8</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>9</v>
       </c>
       <c r="AJ29" t="n">
         <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5683,25 +5750,25 @@
         <v>9</v>
       </c>
       <c r="AN29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS29" t="n">
         <v>26</v>
       </c>
       <c r="AT29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>-2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>22</v>
       </c>
       <c r="AF30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG30" t="n">
         <v>24</v>
@@ -5865,7 +5932,7 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
         <v>17</v>
@@ -5877,7 +5944,7 @@
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5898,7 +5965,7 @@
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
@@ -5939,76 +6006,76 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31" t="n">
         <v>15</v>
       </c>
       <c r="G31" t="n">
-        <v>0.674</v>
+        <v>0.667</v>
       </c>
       <c r="H31" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I31" t="n">
         <v>39.1</v>
       </c>
       <c r="J31" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
         <v>15.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="O31" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="R31" t="n">
         <v>10.3</v>
       </c>
       <c r="S31" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="T31" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="U31" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="V31" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W31" t="n">
         <v>7.6</v>
       </c>
       <c r="X31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y31" t="n">
         <v>4.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB31" t="n">
         <v>99.90000000000001</v>
@@ -6017,10 +6084,10 @@
         <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF31" t="n">
         <v>7</v>
@@ -6029,7 +6096,7 @@
         <v>7</v>
       </c>
       <c r="AH31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6038,7 +6105,7 @@
         <v>20</v>
       </c>
       <c r="AK31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
@@ -6056,28 +6123,28 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
         <v>22</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW31" t="n">
         <v>14</v>
       </c>
       <c r="AX31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6086,7 +6153,7 @@
         <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-27-2014-15</t>
+          <t>2015-01-27</t>
         </is>
       </c>
     </row>
